--- a/data/trans_camb/P16A02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A02-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 5,29</t>
+          <t>-3,83; 5,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 12,53</t>
+          <t>2,03; 12,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 10,78</t>
+          <t>1,54; 11,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 12,27</t>
+          <t>-1,85; 12,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 9,95</t>
+          <t>-3,34; 9,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 17,28</t>
+          <t>4,91; 17,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 6,66</t>
+          <t>-1,23; 6,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,12</t>
+          <t>1,93; 10,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 13,03</t>
+          <t>5,61; 13,35</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 51,08</t>
+          <t>-27,12; 51,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,02; 124,9</t>
+          <t>12,79; 115,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 108,6</t>
+          <t>10,68; 108,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 69,86</t>
+          <t>-8,89; 71,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 58,7</t>
+          <t>-14,45; 55,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,94; 104,17</t>
+          <t>19,58; 102,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 49,4</t>
+          <t>-7,46; 49,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,97; 74,38</t>
+          <t>10,28; 72,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,75; 95,62</t>
+          <t>32,16; 97,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 8,43</t>
+          <t>-3,4; 8,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 7,72</t>
+          <t>-3,97; 7,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 10,31</t>
+          <t>-0,83; 10,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 17,27</t>
+          <t>2,96; 16,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 10,33</t>
+          <t>-3,26; 9,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 14,38</t>
+          <t>2,76; 15,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,28</t>
+          <t>0,88; 9,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 6,88</t>
+          <t>-1,9; 6,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 10,46</t>
+          <t>2,22; 10,45</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 67,38</t>
+          <t>-18,32; 68,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 59,57</t>
+          <t>-21,28; 56,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 82,3</t>
+          <t>-4,96; 74,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 86,8</t>
+          <t>11,56; 81,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 52,58</t>
+          <t>-12,54; 46,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 73,59</t>
+          <t>10,08; 79,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 60,44</t>
+          <t>4,13; 53,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 39,22</t>
+          <t>-8,74; 37,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,31; 62,13</t>
+          <t>10,46; 62,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,65</t>
+          <t>3,42; 12,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 11,56</t>
+          <t>2,85; 11,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 16,59</t>
+          <t>-7,67; 16,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 13,67</t>
+          <t>-4,32; 13,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 22,82</t>
+          <t>2,16; 23,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,31; 33,16</t>
+          <t>14,57; 31,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,85</t>
+          <t>3,61; 11,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 12,63</t>
+          <t>4,03; 12,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 19,0</t>
+          <t>-6,16; 19,08</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,42; 116,58</t>
+          <t>22,98; 113,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,48; 107,78</t>
+          <t>19,28; 108,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,7; 134,77</t>
+          <t>-49,63; 134,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 76,24</t>
+          <t>-14,99; 74,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 118,84</t>
+          <t>6,39; 122,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,87; 178,91</t>
+          <t>50,37; 168,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,02; 89,96</t>
+          <t>20,26; 88,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,47; 92,26</t>
+          <t>23,54; 93,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,37; 127,08</t>
+          <t>-34,82; 130,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,23</t>
+          <t>0,99; 7,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,06</t>
+          <t>0,49; 6,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,71; 15,76</t>
+          <t>8,87; 16,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,55; 12,69</t>
+          <t>3,66; 12,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 11,28</t>
+          <t>2,57; 11,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,33; 52,43</t>
+          <t>15,43; 51,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,54</t>
+          <t>3,47; 8,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,96</t>
+          <t>2,88; 8,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,6; 38,24</t>
+          <t>13,71; 40,29</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,92; 50,11</t>
+          <t>5,23; 48,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,63; 47,03</t>
+          <t>2,87; 45,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,65; 105,43</t>
+          <t>49,12; 105,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,46; 64,54</t>
+          <t>15,37; 66,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,17; 58,24</t>
+          <t>10,74; 59,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,01; 254,84</t>
+          <t>67,2; 260,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,08; 49,86</t>
+          <t>17,66; 50,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,29; 46,26</t>
+          <t>14,36; 46,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72,1; 213,3</t>
+          <t>73,71; 230,52</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 8,95</t>
+          <t>-1,07; 8,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 9,14</t>
+          <t>-0,16; 9,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,47; 18,71</t>
+          <t>7,15; 18,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,99; 16,71</t>
+          <t>5,64; 16,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,1; 14,36</t>
+          <t>3,5; 14,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,91; 23,54</t>
+          <t>5,03; 23,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,3; 11,91</t>
+          <t>4,16; 11,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,04</t>
+          <t>2,38; 9,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,84; 20,22</t>
+          <t>7,43; 20,05</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 77,57</t>
+          <t>-6,77; 77,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 80,15</t>
+          <t>-1,43; 84,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42,76; 166,15</t>
+          <t>39,92; 162,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,29; 71,4</t>
+          <t>19,5; 69,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,39; 61,26</t>
+          <t>11,22; 58,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,88; 93,54</t>
+          <t>19,19; 94,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,48; 59,85</t>
+          <t>17,37; 59,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10,16; 50,59</t>
+          <t>9,64; 49,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>38,64; 99,86</t>
+          <t>33,81; 100,2</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 5,2</t>
+          <t>-2,81; 5,05</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,3; 12,56</t>
+          <t>2,46; 12,52</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,69; 17,75</t>
+          <t>0,81; 17,07</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7,44; 14,86</t>
+          <t>7,67; 15,38</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,02; 11,92</t>
+          <t>4,19; 12,09</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,63; 17,91</t>
+          <t>9,48; 17,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,82</t>
+          <t>6,35; 12,63</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,66; 10,43</t>
+          <t>4,39; 10,95</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,5; 14,97</t>
+          <t>7,41; 14,53</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 125,73</t>
+          <t>-36,98; 125,07</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>27,16; 306,76</t>
+          <t>23,69; 281,38</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0,4; 333,35</t>
+          <t>6,97; 397,62</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27,88; 63,32</t>
+          <t>28,8; 67,15</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15,53; 52,33</t>
+          <t>15,7; 50,64</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35,9; 76,94</t>
+          <t>35,19; 74,33</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,39; 64,17</t>
+          <t>28,11; 64,01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>16,32; 52,37</t>
+          <t>18,91; 54,31</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>32,92; 74,23</t>
+          <t>32,77; 71,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,75</t>
+          <t>2,15; 5,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,6</t>
+          <t>3,16; 6,66</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,52; 11,29</t>
+          <t>3,52; 11,2</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,41; 11,84</t>
+          <t>7,29; 11,74</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,88; 9,36</t>
+          <t>5,12; 9,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,87; 28,53</t>
+          <t>13,91; 29,52</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,41</t>
+          <t>5,36; 8,2</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,51</t>
+          <t>4,61; 7,55</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>10,43; 19,42</t>
+          <t>10,18; 19,65</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>13,91; 44,38</t>
+          <t>14,45; 45,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>21,68; 50,36</t>
+          <t>21,45; 51,11</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26,99; 84,42</t>
+          <t>26,16; 84,97</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29,29; 51,62</t>
+          <t>29,12; 51,24</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>19,31; 40,83</t>
+          <t>19,65; 39,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>56,9; 120,47</t>
+          <t>56,52; 129,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,19; 46,09</t>
+          <t>27,0; 44,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>22,93; 41,16</t>
+          <t>23,42; 41,54</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>53,65; 102,85</t>
+          <t>53,15; 104,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A02-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,29</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,65</t>
+          <t>10,89</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,42</t>
+          <t>9,54</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 5,31</t>
+          <t>-3,51; 5,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 12,04</t>
+          <t>2,69; 12,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 11,18</t>
+          <t>2,69; 11,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 12,28</t>
+          <t>-1,67; 12,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 9,54</t>
+          <t>-2,55; 9,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 17,35</t>
+          <t>4,91; 16,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 6,6</t>
+          <t>-0,68; 6,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 10,12</t>
+          <t>2,22; 9,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 13,35</t>
+          <t>5,77; 13,1</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 51,58</t>
+          <t>-25,7; 48,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,79; 115,07</t>
+          <t>17,19; 124,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,68; 108,33</t>
+          <t>17,5; 113,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 71,15</t>
+          <t>-6,95; 72,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 55,02</t>
+          <t>-10,48; 57,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,58; 102,51</t>
+          <t>19,85; 99,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 49,29</t>
+          <t>-4,08; 48,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 72,7</t>
+          <t>12,73; 72,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,16; 97,96</t>
+          <t>33,85; 96,47</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,27</t>
+          <t>8,92</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,63</t>
+          <t>6,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 8,33</t>
+          <t>-2,74; 8,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 7,28</t>
+          <t>-4,07; 7,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 10,11</t>
+          <t>-1,59; 9,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 16,3</t>
+          <t>2,69; 17,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 9,27</t>
+          <t>-3,05; 9,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 15,31</t>
+          <t>2,83; 14,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,4</t>
+          <t>0,87; 9,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 6,39</t>
+          <t>-1,94; 6,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 10,45</t>
+          <t>2,16; 10,42</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 68,39</t>
+          <t>-15,46; 61,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 56,22</t>
+          <t>-22,35; 57,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 74,33</t>
+          <t>-8,11; 72,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 81,83</t>
+          <t>10,05; 88,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 46,19</t>
+          <t>-12,26; 50,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 79,75</t>
+          <t>10,57; 74,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 53,63</t>
+          <t>3,66; 56,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 37,11</t>
+          <t>-9,22; 40,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 62,3</t>
+          <t>9,87; 62,78</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>14,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,74</t>
+          <t>23,07</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,16</t>
+          <t>17,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 12,5</t>
+          <t>3,67; 13,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,42</t>
+          <t>2,66; 11,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 16,58</t>
+          <t>9,28; 19,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 13,67</t>
+          <t>-3,82; 14,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 23,25</t>
+          <t>1,36; 23,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,57; 31,79</t>
+          <t>13,85; 32,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 11,93</t>
+          <t>3,67; 12,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,03; 12,73</t>
+          <t>3,89; 12,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 19,08</t>
+          <t>13,4; 22,16</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>115,17%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>100,93%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>114,92%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,98; 113,37</t>
+          <t>22,21; 114,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,28; 108,08</t>
+          <t>15,74; 105,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 134,93</t>
+          <t>61,04; 174,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 74,53</t>
+          <t>-14,18; 78,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,39; 122,72</t>
+          <t>2,9; 118,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50,37; 168,86</t>
+          <t>46,81; 173,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,26; 88,19</t>
+          <t>20,82; 93,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,54; 93,8</t>
+          <t>21,16; 92,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 130,3</t>
+          <t>74,27; 166,43</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,43</t>
+          <t>12,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,87</t>
+          <t>17,13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21,56</t>
+          <t>14,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,51</t>
+          <t>0,5; 6,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,68</t>
+          <t>0,42; 6,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,87; 16,01</t>
+          <t>8,68; 15,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 12,85</t>
+          <t>3,91; 13,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 11,6</t>
+          <t>2,71; 11,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,43; 51,62</t>
+          <t>13,08; 21,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,69</t>
+          <t>3,25; 8,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,19</t>
+          <t>2,91; 7,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,71; 40,29</t>
+          <t>11,87; 17,28</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>137,18%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>117,76%</t>
+          <t>79,7%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 48,74</t>
+          <t>2,89; 46,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 45,89</t>
+          <t>2,78; 44,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,12; 105,84</t>
+          <t>49,28; 105,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,37; 66,73</t>
+          <t>16,23; 68,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,74; 59,84</t>
+          <t>10,65; 56,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,2; 260,91</t>
+          <t>54,36; 110,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,66; 50,79</t>
+          <t>16,21; 50,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,36; 46,82</t>
+          <t>15,03; 46,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>73,71; 230,52</t>
+          <t>60,66; 101,9</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13,25</t>
+          <t>11,39</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,58</t>
+          <t>20,97</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,63</t>
+          <t>16,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 8,6</t>
+          <t>-1,17; 8,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 9,39</t>
+          <t>-0,06; 9,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,15; 18,57</t>
+          <t>5,8; 16,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,64; 16,61</t>
+          <t>5,75; 16,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,5; 14,01</t>
+          <t>3,86; 14,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,03; 23,29</t>
+          <t>15,92; 25,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,58</t>
+          <t>4,06; 11,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 9,92</t>
+          <t>2,65; 10,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,43; 20,05</t>
+          <t>13,29; 20,39</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 77,82</t>
+          <t>-7,08; 76,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 84,91</t>
+          <t>-1,62; 88,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39,92; 162,9</t>
+          <t>33,79; 144,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,5; 69,77</t>
+          <t>19,74; 69,79</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,22; 58,57</t>
+          <t>12,89; 57,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,19; 94,17</t>
+          <t>51,95; 107,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,37; 59,25</t>
+          <t>16,69; 59,81</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,64; 49,67</t>
+          <t>10,95; 50,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>33,81; 100,2</t>
+          <t>53,93; 101,89</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,58</t>
+          <t>12,67</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11,08</t>
+          <t>10,49</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 5,05</t>
+          <t>-3,09; 4,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,46; 12,52</t>
+          <t>1,45; 12,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,81; 17,07</t>
+          <t>-0,68; 12,77</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7,67; 15,38</t>
+          <t>7,43; 14,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,19; 12,09</t>
+          <t>4,34; 11,6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,48; 17,36</t>
+          <t>8,84; 16,28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,63</t>
+          <t>6,23; 12,96</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,95</t>
+          <t>4,01; 10,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,41; 14,53</t>
+          <t>7,02; 14,05</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114,46%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>49,26%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 125,07</t>
+          <t>-39,73; 115,37</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>23,69; 281,38</t>
+          <t>16,18; 280,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6,97; 397,62</t>
+          <t>-12,24; 286,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28,8; 67,15</t>
+          <t>27,77; 63,68</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15,7; 50,64</t>
+          <t>16,5; 50,95</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35,19; 74,33</t>
+          <t>32,85; 70,29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28,11; 64,01</t>
+          <t>27,29; 64,8</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>18,91; 54,31</t>
+          <t>17,54; 54,81</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>32,77; 71,82</t>
+          <t>30,45; 69,8</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8,7</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,31</t>
+          <t>15,31</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,7</t>
+          <t>12,8</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,87</t>
+          <t>2,29; 5,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,66</t>
+          <t>3,05; 6,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,52; 11,2</t>
+          <t>8,0; 11,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,29; 11,74</t>
+          <t>7,31; 11,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,23</t>
+          <t>4,94; 9,56</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,91; 29,52</t>
+          <t>13,21; 17,29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,2</t>
+          <t>5,46; 8,33</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,55</t>
+          <t>4,81; 7,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>10,18; 19,65</t>
+          <t>11,26; 14,11</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,45; 45,19</t>
+          <t>15,37; 44,25</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>21,45; 51,11</t>
+          <t>20,5; 51,53</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26,16; 84,97</t>
+          <t>55,07; 91,75</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29,12; 51,24</t>
+          <t>29,14; 52,39</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>19,65; 39,94</t>
+          <t>19,77; 42,34</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>56,52; 129,14</t>
+          <t>52,43; 76,4</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,0; 44,66</t>
+          <t>27,76; 45,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>23,42; 41,54</t>
+          <t>24,46; 41,89</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>53,15; 104,37</t>
+          <t>56,98; 77,26</t>
         </is>
       </c>
     </row>
